--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74246933</v>
       </c>
       <c r="B2" t="n">
-        <v>96953</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445346.3529753603</v>
+        <v>445346</v>
       </c>
       <c r="R2" t="n">
-        <v>6406781.642097725</v>
+        <v>6406782</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1980-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74208262</v>
       </c>
       <c r="B3" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445346.3529753603</v>
+        <v>445346</v>
       </c>
       <c r="R3" t="n">
-        <v>6406781.642097725</v>
+        <v>6406782</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1980-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74478748</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445346.3529753603</v>
+        <v>445346</v>
       </c>
       <c r="R4" t="n">
-        <v>6406781.642097725</v>
+        <v>6406782</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1980-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1056,12 +1011,7 @@
         <v>74604213</v>
       </c>
       <c r="B5" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445247.7803843439</v>
+        <v>445248</v>
       </c>
       <c r="R5" t="n">
-        <v>6406680.112151444</v>
+        <v>6406680</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,19 +1076,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1182,12 +1122,7 @@
         <v>74843671</v>
       </c>
       <c r="B6" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445147.9059296344</v>
+        <v>445148</v>
       </c>
       <c r="R6" t="n">
-        <v>6406679.340160362</v>
+        <v>6406679</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1252,19 +1187,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74246933</v>
       </c>
       <c r="B2" t="n">
-        <v>99242</v>
+        <v>99247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208262</v>
       </c>
       <c r="B3" t="n">
-        <v>99215</v>
+        <v>99220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74478748</v>
       </c>
       <c r="B4" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74843671</v>
       </c>
       <c r="B6" t="n">
-        <v>105554</v>
+        <v>105563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74246933</v>
       </c>
       <c r="B2" t="n">
-        <v>99247</v>
+        <v>99248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208262</v>
       </c>
       <c r="B3" t="n">
-        <v>99220</v>
+        <v>99221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74478748</v>
       </c>
       <c r="B4" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74604213</v>
       </c>
       <c r="B5" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74843671</v>
       </c>
       <c r="B6" t="n">
-        <v>105563</v>
+        <v>105566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74246933</v>
       </c>
       <c r="B2" t="n">
-        <v>99248</v>
+        <v>99275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208262</v>
       </c>
       <c r="B3" t="n">
-        <v>99221</v>
+        <v>99248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74478748</v>
       </c>
       <c r="B4" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74604213</v>
       </c>
       <c r="B5" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74843671</v>
       </c>
       <c r="B6" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74246933</v>
       </c>
       <c r="B2" t="n">
-        <v>99275</v>
+        <v>99281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208262</v>
       </c>
       <c r="B3" t="n">
-        <v>99248</v>
+        <v>99254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74478748</v>
       </c>
       <c r="B4" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74604213</v>
       </c>
       <c r="B5" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74843671</v>
       </c>
       <c r="B6" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74246933</v>
       </c>
       <c r="B2" t="n">
-        <v>99281</v>
+        <v>99288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208262</v>
       </c>
       <c r="B3" t="n">
-        <v>99254</v>
+        <v>99261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74478748</v>
       </c>
       <c r="B4" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74604213</v>
       </c>
       <c r="B5" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74843671</v>
       </c>
       <c r="B6" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74246933</v>
       </c>
       <c r="B2" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208262</v>
       </c>
       <c r="B3" t="n">
-        <v>99261</v>
+        <v>99265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74478748</v>
       </c>
       <c r="B4" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74604213</v>
       </c>
       <c r="B5" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74843671</v>
       </c>
       <c r="B6" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74246933</v>
       </c>
       <c r="B2" t="n">
-        <v>99292</v>
+        <v>99299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208262</v>
       </c>
       <c r="B3" t="n">
-        <v>99265</v>
+        <v>99272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74478748</v>
       </c>
       <c r="B4" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74604213</v>
       </c>
       <c r="B5" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74843671</v>
       </c>
       <c r="B6" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74246933</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208262</v>
       </c>
       <c r="B3" t="n">
-        <v>99275</v>
+        <v>99280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74478748</v>
       </c>
       <c r="B4" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74604213</v>
       </c>
       <c r="B5" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74843671</v>
       </c>
       <c r="B6" t="n">
-        <v>105621</v>
+        <v>105626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74246933</v>
       </c>
       <c r="B2" t="n">
-        <v>99307</v>
+        <v>99315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208262</v>
       </c>
       <c r="B3" t="n">
-        <v>99280</v>
+        <v>99288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74478748</v>
       </c>
       <c r="B4" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74604213</v>
       </c>
       <c r="B5" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74843671</v>
       </c>
       <c r="B6" t="n">
-        <v>105626</v>
+        <v>105634</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74246933</v>
       </c>
       <c r="B2" t="n">
-        <v>99315</v>
+        <v>99325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208262</v>
       </c>
       <c r="B3" t="n">
-        <v>99288</v>
+        <v>99298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74478748</v>
       </c>
       <c r="B4" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74604213</v>
       </c>
       <c r="B5" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74843671</v>
       </c>
       <c r="B6" t="n">
-        <v>105634</v>
+        <v>105644</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74246933</v>
+        <v>102951572</v>
       </c>
       <c r="B2" t="n">
-        <v>99325</v>
+        <v>91087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222309</v>
+        <v>4823</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Hasselsopp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Leccinellum pseudoscabrum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Kallenb.) Mikšík</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Toveryd. 600m NV Stora Toveryd.Sågbäcken, Sm</t>
+          <t>Skams hål, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445346</v>
+        <v>445347</v>
       </c>
       <c r="R2" t="n">
-        <v>6406782</v>
+        <v>6406616</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1980-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7D1j 4624. SOM: Carex ericetorum. LEG: Sigurd Jerkeman</t>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,73 +776,78 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandskog, bäck</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74208262</v>
+        <v>112038078</v>
       </c>
       <c r="B3" t="n">
-        <v>99298</v>
+        <v>91683</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222295</v>
+        <v>5678</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Kruskantarell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Craterellus undulatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) E.Campo &amp; Papetti</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Toveryd. 600m NV Stora Toveryd.Sågbäcken, Sm</t>
+          <t>Lallerydsbäcken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445346</v>
+        <v>445227</v>
       </c>
       <c r="R3" t="n">
-        <v>6406782</v>
+        <v>6406697</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,17 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1980-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7D1j 4624. SOM: Carex caryophyllea. LEG: Sigurd Jerkeman</t>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,34 +898,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandskog, bäck</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Hassel</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Sofie Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Sofie Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74478748</v>
+        <v>74843671</v>
       </c>
       <c r="B4" t="n">
-        <v>100857</v>
+        <v>106155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,34 +929,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Toveryd. 600m NV Stora Toveryd.Sågbäcken, Sm</t>
+          <t>L50 Rustorp 500 m OSO, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445346</v>
+        <v>445148</v>
       </c>
       <c r="R4" t="n">
-        <v>6406782</v>
+        <v>6406679</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -962,17 +983,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1980-12-31</t>
+          <t>1991-12-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7D1j 4624. SOM: Hepatica nobilis. LEG: Sigurd Jerkeman</t>
+          <t>Smålands flora 2007: KOO: 7D1j 4522. SOM: Primula veris. LEG: Lennart Persson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Blandskog, bäck</t>
+          <t>Hasselsluttning-betesmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,7 +1032,7 @@
         <v>74604213</v>
       </c>
       <c r="B5" t="n">
-        <v>97543</v>
+        <v>97986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,45 +1140,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74843671</v>
+        <v>74208262</v>
       </c>
       <c r="B6" t="n">
-        <v>105644</v>
+        <v>99754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221141</v>
+        <v>222295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>L50 Rustorp 500 m OSO, Sm</t>
+          <t>Toveryd. 600m NV Stora Toveryd.Sågbäcken, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445148</v>
+        <v>445346</v>
       </c>
       <c r="R6" t="n">
-        <v>6406679</v>
+        <v>6406782</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1184,17 +1205,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1987-01-01</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1991-12-31</t>
+          <t>1980-12-31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7D1j 4522. SOM: Primula veris. LEG: Lennart Persson</t>
+          <t>Smålands flora 2007: KOO: 7D1j 4624. SOM: Carex caryophyllea. LEG: Sigurd Jerkeman</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1229,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Hasselsluttning-betesmark</t>
+          <t>Blandskog, bäck</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,63 +1251,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102951572</v>
+        <v>74246933</v>
       </c>
       <c r="B7" t="n">
-        <v>88617</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4823</v>
+        <v>222309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hasselsopp</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leccinellum pseudoscabrum</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kallenb.) Mikšík</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skams hål, Sm</t>
+          <t>Toveryd. 600m NV Stora Toveryd.Sågbäcken, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445347.298516839</v>
+        <v>445346</v>
       </c>
       <c r="R7" t="n">
-        <v>6406615.330589094</v>
+        <v>6406782</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,22 +1316,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:51</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:51</t>
+          <t>1980-12-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7D1j 4624. SOM: Carex ericetorum. LEG: Sigurd Jerkeman</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,19 +1337,139 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandskog, bäck</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>74478748</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Toveryd. 600m NV Stora Toveryd.Sågbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>445346</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6406782</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1980-12-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7D1j 4624. SOM: Hepatica nobilis. LEG: Sigurd Jerkeman</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Blandskog, bäck</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6205-2025 artfynd.xlsx
+++ b/artfynd/A 6205-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102951572</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038078</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74843671</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74604213</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74208262</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74246933</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,8 +1505,22 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74478748</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>